--- a/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
@@ -632,14 +632,13 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -656,13 +655,14 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -698,12 +698,13 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">30226
 </t>
         </is>
       </c>
@@ -715,7 +716,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -727,13 +728,14 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -750,7 +752,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -774,7 +776,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">623
 </t>
         </is>
       </c>
@@ -786,7 +788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -798,7 +800,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -816,7 +818,8 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -833,8 +836,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -845,19 +847,19 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -875,19 +877,18 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>616</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -904,8 +905,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">4316
 </t>
         </is>
       </c>
@@ -952,13 +952,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -968,10 +968,16 @@
 </t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">606
+</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -982,7 +988,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -1000,7 +1006,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1030,7 +1036,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -1054,12 +1060,12 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1089,12 +1095,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -1106,8 +1112,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1124,31 +1129,31 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">060
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1502
+</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">173
 </t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1173
-</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8726
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -1160,7 +1165,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">3189
 </t>
         </is>
       </c>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -1190,30 +1195,30 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -1231,26 +1236,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2972
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>526</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1261,13 +1262,13 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1278,8 +1279,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">18656
 </t>
         </is>
       </c>
@@ -1302,13 +1302,13 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1350,25 +1350,25 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1385,42 +1385,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66631</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925
-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">925
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">601
-</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1431,19 +1426,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">443
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -1461,7 +1454,8 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1477,7 +1471,8 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t xml:space="preserve">319
+</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -1500,18 +1495,19 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">024
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1535,8 +1531,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333
-</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1547,7 +1542,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1558,14 +1553,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1576,11 +1569,15 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5447
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -1589,13 +1586,13 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1613,8 +1610,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -1625,31 +1621,29 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1661,7 +1655,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">8065
 </t>
         </is>
       </c>
@@ -1685,19 +1679,18 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450
+          <t xml:space="preserve">4456
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
@@ -1709,7 +1702,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
@@ -1721,13 +1714,13 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1748,7 +1741,12 @@
 </t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">879
@@ -1769,7 +1767,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -1781,7 +1779,8 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t xml:space="preserve">850
+</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1804,13 +1803,13 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2309
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -1846,8 +1845,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1858,8 +1856,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1900,7 +1897,8 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1911,19 +1909,19 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">2722
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -1941,19 +1939,17 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -1971,7 +1967,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -1989,8 +1985,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2567
-</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2019,7 +2014,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2037,7 +2032,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -2055,14 +2050,13 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2073,7 +2067,7 @@
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">4286
 </t>
         </is>
       </c>
@@ -2085,7 +2079,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">3247
 </t>
         </is>
       </c>
@@ -2103,14 +2097,13 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
@@ -2121,8 +2114,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2145,7 +2137,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">3408
 </t>
         </is>
       </c>
@@ -2157,7 +2149,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2169,13 +2161,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2193,25 +2185,25 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -2235,13 +2227,13 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2277,7 +2269,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2306,20 +2298,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>418</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2348,25 +2337,24 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -2414,7 +2402,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -2426,19 +2414,18 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -2456,19 +2443,19 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19928
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">9291
 </t>
         </is>
       </c>
@@ -2510,26 +2497,31 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
+          <t xml:space="preserve">1609
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9186
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211222
+</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2540,12 +2532,14 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t xml:space="preserve">425
+</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2556,8 +2550,7 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2568,23 +2561,24 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>464</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -2602,7 +2596,9 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t xml:space="preserve">1
+3986
+</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2619,32 +2615,28 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
@@ -2662,7 +2654,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2686,50 +2678,57 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">2428
+</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2744,35 +2743,36 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1373
+          <t xml:space="preserve">432
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2783,13 +2783,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2801,7 +2800,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -2813,13 +2812,13 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2429
 </t>
         </is>
       </c>
@@ -2831,7 +2830,8 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">231
+</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2842,12 +2842,13 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>044</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2870,13 +2871,14 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">46
+8 179
 </t>
         </is>
       </c>
@@ -2918,20 +2920,19 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2942,8 +2943,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2954,13 +2954,13 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3008,8 +3008,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -3020,18 +3019,21 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">212
+44
+</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">62
+818
 </t>
         </is>
       </c>
@@ -3049,40 +3051,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568
-</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t xml:space="preserve">235
+</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">3
+1 8 4
+7
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -3094,13 +3098,12 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -3118,20 +3121,17 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -3148,14 +3148,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -3166,23 +3164,21 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="2" t="n"/>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
           <t>13</t>
@@ -3203,8 +3199,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3219,14 +3214,10 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3244,7 +3235,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -3256,7 +3247,8 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3285,19 +3277,19 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">417
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">5310
 </t>
         </is>
       </c>
@@ -3309,23 +3301,25 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t xml:space="preserve">259
+8111
+</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3348,25 +3342,24 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3377,7 +3370,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -3401,7 +3394,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3413,13 +3406,13 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">8720
 </t>
         </is>
       </c>
@@ -3449,8 +3442,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -3461,25 +3453,24 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -3503,20 +3494,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19255
-</t>
+          <t>19855</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3527,13 +3515,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">603
-</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
@@ -3563,7 +3550,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">8826
 </t>
         </is>
       </c>
@@ -3575,67 +3562,71 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4372
+          <t xml:space="preserve">4382
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
+          <t xml:space="preserve">1462
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>43</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t xml:space="preserve">29526
+</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t xml:space="preserve">854
+</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t xml:space="preserve">107
+</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3653,8 +3644,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3851
-</t>
+          <t>58511</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3665,7 +3655,8 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3676,13 +3667,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -3698,7 +3688,7 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -3707,25 +3697,25 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">8724
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -3755,13 +3745,13 @@
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -3773,17 +3763,19 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t xml:space="preserve">9
+</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">5
+</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3800,48 +3792,54 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">3261
+</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3853,13 +3851,13 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2604
 </t>
         </is>
       </c>
@@ -3871,31 +3869,30 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3906,7 +3903,8 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">71
+</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3917,8 +3915,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3929,7 +3926,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3947,8 +3944,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
-</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3965,31 +3961,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>363</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -4001,7 +4002,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>181</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4012,19 +4013,19 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -4036,20 +4037,19 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -4078,7 +4078,8 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">16
+54
 </t>
         </is>
       </c>
@@ -4096,17 +4097,19 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">284
+</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -4117,18 +4120,19 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4140,31 +4144,30 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
@@ -4188,50 +4191,45 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">684
+</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2426
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">684
-</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
-        </is>
-      </c>
-      <c r="Z27" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
+          <t>081</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="n"/>
       <c r="AA27" t="inlineStr">
         <is>
           <t>18</t>
@@ -4252,14 +4250,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -4270,19 +4266,19 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4294,7 +4290,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
@@ -4318,13 +4314,13 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">824
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4342,7 +4338,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4354,35 +4350,36 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>635</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t xml:space="preserve">820
+</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4399,64 +4396,59 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4085
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12396
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">203
 </t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192
@@ -4477,7 +4469,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4495,7 +4487,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4507,13 +4499,13 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4530,7 +4522,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -4552,15 +4544,10 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">856
-</t>
-        </is>
-      </c>
+      <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4578,19 +4565,18 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4602,7 +4588,8 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4613,20 +4600,18 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
-</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4637,37 +4622,36 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3328
-</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">643
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4684,7 +4668,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
+          <t xml:space="preserve">3228
 </t>
         </is>
       </c>
@@ -4708,19 +4692,18 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3713
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4732,7 +4715,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -4744,7 +4727,8 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -4753,22 +4737,27 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4785,7 +4774,7 @@
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4797,24 +4786,25 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
@@ -4826,19 +4816,18 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -4862,7 +4851,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -4874,12 +4863,14 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -4890,7 +4881,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -4900,29 +4891,31 @@
 </t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>816</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4933,19 +4926,17 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -4957,37 +4948,36 @@
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">637
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">621
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">2
+78
 </t>
         </is>
       </c>
@@ -5005,7 +4995,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3970
+          <t xml:space="preserve">32720
 </t>
         </is>
       </c>
@@ -5022,37 +5012,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -5064,26 +5053,24 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -5100,7 +5087,7 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5112,7 +5099,7 @@
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -5124,24 +5111,25 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5158,19 +5146,18 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3624
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">3604
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -5182,31 +5169,30 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5218,25 +5204,25 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -5248,13 +5234,13 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5266,34 +5252,39 @@
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>455</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>885</t>
-        </is>
-      </c>
-      <c r="Z34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">832
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+5
+</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>23</t>
@@ -5308,8 +5299,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -5332,8 +5322,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -5345,105 +5334,98 @@
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2216
+</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">203
 </t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">854
-</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">885
-</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>836</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -5464,13 +5446,13 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t xml:space="preserve">286
+</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -5481,8 +5463,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -5499,49 +5480,49 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">2890
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -5571,29 +5552,25 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">248
+</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3966
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -5617,23 +5594,25 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0029</t>
+          <t xml:space="preserve">059
+</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t xml:space="preserve">355
+</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -5651,101 +5630,100 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t xml:space="preserve">1035
+</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9251
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1078
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
+          <t xml:space="preserve">4325
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13996
-</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>26201</t>
+          <t xml:space="preserve">627
+</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3437
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">657
-</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
+          <t xml:space="preserve">3266
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5768,13 +5746,13 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">3600
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2646
 </t>
         </is>
       </c>
@@ -5786,13 +5764,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
@@ -5804,13 +5782,13 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -5822,14 +5800,13 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -5840,13 +5817,12 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -5870,27 +5846,35 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="n"/>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2526
+</t>
+        </is>
+      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">793
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
@@ -5908,12 +5892,13 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>427</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">318
+</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -5930,7 +5915,8 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -5941,42 +5927,52 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>155</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>415</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -5988,8 +5984,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
@@ -6000,36 +5995,36 @@
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t xml:space="preserve">6
+</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6046,7 +6041,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -6058,7 +6053,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2024
 </t>
         </is>
       </c>
@@ -6070,7 +6065,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -6082,20 +6077,18 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">2064
 </t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -6106,31 +6099,31 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001
+          <t xml:space="preserve">2221
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">2160
 </t>
         </is>
       </c>
@@ -6166,25 +6159,23 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6201,18 +6192,19 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4488
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -6224,31 +6216,30 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -6260,13 +6251,13 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -6278,7 +6269,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -6320,25 +6311,25 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">813
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6355,71 +6346,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">442
+2 6
+</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>331</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>0401</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1781
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -6431,13 +6423,13 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -6449,7 +6441,7 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -6461,36 +6453,36 @@
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6513,25 +6505,22 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -6549,13 +6538,13 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6567,7 +6556,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -6585,7 +6574,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -6615,36 +6604,36 @@
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>632</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">244
+</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t xml:space="preserve">820
+</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6667,13 +6656,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -6685,7 +6673,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -6697,30 +6685,30 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -6750,48 +6738,48 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>663</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9223
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>611</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y44" s="2" t="n"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -6810,84 +6798,103 @@
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0564</t>
-        </is>
-      </c>
+          <t xml:space="preserve">777
+</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n"/>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>677</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t xml:space="preserve">372
+</t>
         </is>
       </c>
       <c r="P45" s="2" t="n"/>
-      <c r="Q45" s="2" t="n"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">70
+</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t xml:space="preserve">7335
+</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -6898,7 +6905,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -6910,7 +6917,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
@@ -6928,8 +6935,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -6946,7 +6952,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">2480
 </t>
         </is>
       </c>
@@ -6958,7 +6964,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -6970,11 +6976,16 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1656
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -6983,13 +6994,13 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18256
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">20 8
 </t>
         </is>
       </c>
@@ -7013,16 +7024,11 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="n"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">690
@@ -7037,14 +7043,30 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">2424
 </t>
         </is>
       </c>
       <c r="W46" s="2" t="n"/>
-      <c r="X46" s="2" t="n"/>
-      <c r="Y46" s="2" t="inlineStr"/>
-      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1242
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 7
+57
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -7057,15 +7079,34 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1111
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,36 +626,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">94375
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1312
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -667,7 +665,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -680,50 +678,49 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30226
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">637
-</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -734,8 +731,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -744,24 +740,9 @@
 </t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -774,51 +755,41 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">623
-</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
@@ -836,30 +807,26 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
-</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -871,46 +838,44 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="n"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t xml:space="preserve">741
+</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -928,13 +893,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4316
-</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
@@ -952,43 +916,38 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">606
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1203
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -1000,37 +959,36 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">12329
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">16089
 </t>
         </is>
       </c>
@@ -1042,30 +1000,31 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t xml:space="preserve">1850
+</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -1083,77 +1042,71 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">14373
 </t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">2330
 </t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1648
+</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">060
-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1502
-</t>
-        </is>
-      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1673
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">1876
 </t>
         </is>
       </c>
@@ -1165,7 +1118,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3189
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1177,13 +1130,13 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">20221
 </t>
         </is>
       </c>
@@ -1195,30 +1148,31 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">1276
+</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1779
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -1236,22 +1190,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">12972
+</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t xml:space="preserve">1262
+</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1262,13 +1220,14 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1279,66 +1238,66 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>245</t>
+          <t xml:space="preserve">1285
+</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18656
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">1205
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
+          <t xml:space="preserve">1877
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">1332
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1356,19 +1315,20 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1385,39 +1345,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">16665
 </t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">925
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8526
+</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t xml:space="preserve">805
+</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">155
@@ -1426,58 +1377,61 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">443
+</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t xml:space="preserve">1943
+</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
+          <t xml:space="preserve">1963
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4409
+          <t xml:space="preserve">14409
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1629
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
+          <t xml:space="preserve">11388
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t xml:space="preserve">16173
+</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">1329
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
+          <t xml:space="preserve">13609
 </t>
         </is>
       </c>
@@ -1489,31 +1443,16 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11261
+</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="n"/>
+      <c r="X9" s="2" t="n"/>
+      <c r="Y9" s="2" t="n"/>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1531,18 +1470,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t xml:space="preserve">3333
+</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">3051
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1553,12 +1493,14 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">1161
+</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1569,36 +1511,27 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5447
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1876
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
@@ -1610,40 +1543,42 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t xml:space="preserve">278
+</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">1264
+</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">2722
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">117
+</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1655,13 +1590,13 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8065
+          <t xml:space="preserve">1805
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -1679,30 +1614,31 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456
+          <t xml:space="preserve">14450
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">287
+</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1714,12 +1650,13 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -1729,12 +1666,7 @@
 </t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
+      <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">187
@@ -1743,26 +1675,25 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">1879
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>419</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1773,7 +1704,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">19819
 </t>
         </is>
       </c>
@@ -1785,19 +1716,19 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">1357
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
@@ -1809,16 +1740,11 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1975
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1845,18 +1771,20 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1867,7 +1795,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -1879,14 +1807,13 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1909,13 +1836,13 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2722
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
@@ -1933,41 +1860,42 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>85441</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t xml:space="preserve">53
+</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">1247
+</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">12844
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">2304
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
+          <t xml:space="preserve">1977
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -1985,12 +1913,13 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t xml:space="preserve">393567
+</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
@@ -2014,31 +1943,31 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1176
+</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
@@ -2056,18 +1985,14 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1891
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -2079,7 +2004,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3247
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
@@ -2091,30 +2016,32 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">1614
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">1238
+</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1929
+</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2137,19 +2064,19 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
+          <t xml:space="preserve">139740
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">1325
 </t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2161,43 +2088,38 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -2209,7 +2131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
@@ -2227,13 +2149,13 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2263,13 +2185,14 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t xml:space="preserve">1930
+</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2298,28 +2221,31 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t xml:space="preserve">295
+</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t xml:space="preserve">1208
+</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">1249
+</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -2331,19 +2257,18 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -2352,15 +2277,10 @@
           <t>9</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
+      <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -2384,13 +2304,13 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
+          <t xml:space="preserve">1638
 </t>
         </is>
       </c>
@@ -2402,30 +2322,31 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">12411
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t xml:space="preserve">1740
+</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -2443,19 +2364,19 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">119928
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">1499
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9291
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
@@ -2467,22 +2388,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
+          <t xml:space="preserve">1508
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1903
+</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -2491,13 +2407,13 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1609
+          <t xml:space="preserve">11009
 </t>
         </is>
       </c>
@@ -2509,48 +2425,49 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211222
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">4441
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">11428
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">1425
 </t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3687
+          <t xml:space="preserve">13687
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5334415</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2559,26 +2476,17 @@
 </t>
         </is>
       </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
+      <c r="W16" s="2" t="n"/>
+      <c r="X16" s="2" t="n"/>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
+          <t xml:space="preserve">14551
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -2596,9 +2504,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-3986
-</t>
+          <t>399</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2615,7 +2521,8 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">12249
+</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2625,42 +2532,44 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -2672,36 +2581,36 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2861
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">1737
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">1106
+</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2428
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
@@ -2713,19 +2622,19 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -2743,7 +2652,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">432
+          <t xml:space="preserve">4375
 </t>
         </is>
       </c>
@@ -2755,40 +2664,38 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1249
+</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">1871
+</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1395
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">40
+</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -2812,19 +2719,19 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2429
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -2836,30 +2743,31 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t xml:space="preserve">1631
+</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">2256
 </t>
         </is>
       </c>
@@ -2871,14 +2779,13 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-8 179
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2896,7 +2803,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4239
+          <t xml:space="preserve">14239
 </t>
         </is>
       </c>
@@ -2914,36 +2821,38 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">11248
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2954,25 +2863,24 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2996,8 +2904,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>621</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -3008,7 +2915,8 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t xml:space="preserve">1258
+</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -3019,21 +2927,19 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-44
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-818
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3051,42 +2957,43 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t xml:space="preserve">2568
+</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-1 8 4
-7
+          <t xml:space="preserve">1822
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3098,45 +3005,49 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t xml:space="preserve">124080
+</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">1890
+</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -3148,12 +3059,14 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t xml:space="preserve">707
+</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -3164,21 +3077,28 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t xml:space="preserve">1205
+</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="Z20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1672
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>13</t>
@@ -3193,13 +3113,14 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335
+          <t xml:space="preserve">14335
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">1308
+</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3214,16 +3135,21 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3233,12 +3159,7 @@
 </t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">188
@@ -3247,8 +3168,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3259,37 +3179,32 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1867
+</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">1301
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">417
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5310
+          <t xml:space="preserve">1510
 </t>
         </is>
       </c>
@@ -3301,30 +3216,30 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">1243
+</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">259
-8111
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t xml:space="preserve">1850
+</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3342,24 +3257,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">374 0
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>312</t>
+          <t xml:space="preserve">318
+</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3370,19 +3287,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -3394,7 +3311,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -3406,19 +3323,19 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8720
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -3436,13 +3353,14 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t xml:space="preserve">1564
+</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -3453,24 +3371,25 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">1855
 </t>
         </is>
       </c>
@@ -3494,28 +3413,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t xml:space="preserve">19255
+</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t xml:space="preserve">1531
+</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">928
+</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">11230
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t xml:space="preserve">1603
+</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -3532,101 +3455,83 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1355
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">499
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">1952
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8826
+          <t xml:space="preserve">18828
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4382
+          <t xml:space="preserve">14372
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1462
-</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29526
+          <t xml:space="preserve">12952
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="n"/>
+      <c r="W23" s="2" t="n"/>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">11267
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">14110
+</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -3644,7 +3549,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>58511</t>
+          <t xml:space="preserve">3851
+</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3661,18 +3567,19 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2246
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
@@ -3697,31 +3604,26 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8724
-</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1874
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -3739,19 +3641,19 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">1590
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
@@ -3763,19 +3665,19 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1822
+</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3792,31 +3694,31 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">13740
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3261
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">1257
+</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3833,16 +3735,11 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">195
@@ -3851,13 +3748,13 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2604
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
@@ -3869,64 +3766,66 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t xml:space="preserve">1313
+</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t xml:space="preserve">9569
+</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">12242
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">1226
+</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">17476
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -3944,7 +3843,8 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t xml:space="preserve">3298
+</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3961,68 +3861,69 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1720
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19492
+</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1870
+</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">128
 </t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">872
-</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">244
@@ -4037,13 +3938,13 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
@@ -4054,32 +3955,30 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-54
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -4097,12 +3996,13 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t xml:space="preserve">8
+</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -4114,72 +4014,68 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t xml:space="preserve">7208
+</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">1875
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">2060
 </t>
         </is>
       </c>
@@ -4191,13 +4087,13 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
@@ -4209,27 +4105,33 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">1208
+</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>081</t>
-        </is>
-      </c>
-      <c r="Z27" s="2" t="n"/>
+          <t xml:space="preserve">1808
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>18</t>
@@ -4244,18 +4146,20 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3893
+          <t xml:space="preserve">93893
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">298
+</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -4266,13 +4170,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -4284,46 +4188,46 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1398
+</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1213
+</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1874
+</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
 </t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">282
@@ -4332,30 +4236,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">1649
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -4378,7 +4284,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -4396,50 +4302,55 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t xml:space="preserve">4085
+</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">201
+</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">167
+</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12396
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -4457,7 +4368,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1213
 </t>
         </is>
       </c>
@@ -4469,13 +4380,13 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -4487,13 +4398,13 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">12265
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">1626
 </t>
         </is>
       </c>
@@ -4505,7 +4416,8 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>260</t>
+          <t xml:space="preserve">1255
+</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4522,13 +4434,13 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -4544,10 +4456,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18564
+</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1503
 </t>
         </is>
       </c>
@@ -4565,93 +4482,98 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">1525
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t xml:space="preserve">1919
+</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t xml:space="preserve">11032
+</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">14419
+</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">11385
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">11137
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t xml:space="preserve">13328
+</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">1645
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t xml:space="preserve">18231
+</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4662,19 +4584,19 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">11243
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">13998
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
@@ -4692,18 +4614,18 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -4715,14 +4637,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4733,48 +4653,43 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>064</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
@@ -4786,13 +4701,13 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">1666
 </t>
         </is>
       </c>
@@ -4804,30 +4719,31 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t xml:space="preserve">800
+</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -4851,133 +4767,127 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+          <t>8651</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">310
+</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t xml:space="preserve">1240
+</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
+          <t xml:space="preserve">1566
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">637
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1264
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-78
+          <t xml:space="preserve">11188
 </t>
         </is>
       </c>
@@ -4995,53 +4905,48 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32720
+          <t xml:space="preserve">13970
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">337
+</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5053,29 +4958,30 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>495</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">1329
 </t>
         </is>
       </c>
@@ -5087,49 +4993,49 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">477
+          <t xml:space="preserve">19477
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">258
 </t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5146,18 +5052,19 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t xml:space="preserve">3624
+</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3604
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -5169,31 +5076,31 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -5204,28 +5111,23 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1873
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">261
@@ -5234,13 +5136,13 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
@@ -5252,36 +5154,36 @@
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>0554</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t xml:space="preserve">233
+</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">1832
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-5
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -5299,30 +5201,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t xml:space="preserve">1879
+</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -5331,101 +5235,113 @@
 </t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t xml:space="preserve">2010
+</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">2093
+</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1243
+</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1216
+</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1885
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
 </t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">885
-</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2216
-</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="X35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -5446,24 +5362,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t xml:space="preserve">1200
+</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -5480,13 +5398,13 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5498,43 +5416,43 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">25938
 </t>
         </is>
       </c>
@@ -5552,25 +5470,31 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2050
+</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1221
+</t>
+        </is>
+      </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">1782
+</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5588,37 +5512,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16835
-</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">561
-</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">059
-</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">355
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">116835
+</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">1924
 </t>
         </is>
       </c>
@@ -5630,13 +5539,13 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1608
 </t>
         </is>
       </c>
@@ -5646,54 +5555,47 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1172
-</t>
-        </is>
-      </c>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4325
+          <t xml:space="preserve">14325
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t xml:space="preserve">1396
+</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">1154
+</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">627
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>34311</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t xml:space="preserve">1657
+</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -5702,27 +5604,17 @@
 </t>
         </is>
       </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">721
-</t>
-        </is>
-      </c>
+      <c r="W37" s="2" t="n"/>
+      <c r="X37" s="2" t="n"/>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3266
+          <t xml:space="preserve">3966
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">3424
 </t>
         </is>
       </c>
@@ -5746,52 +5638,45 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3600
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2646
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12111
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -5800,29 +5685,31 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">1875
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">390
+</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
@@ -5834,36 +5721,38 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1252
+</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1687
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">252
 </t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">687
-</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2526
-</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -5874,7 +5763,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -5892,7 +5781,8 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t xml:space="preserve">14008
+</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5903,76 +5793,79 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">525
+</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1205
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">195
 </t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">910
+</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">1304
 </t>
         </is>
       </c>
@@ -5984,13 +5877,13 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -6001,29 +5894,31 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t xml:space="preserve">1268
+</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">784
+</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -6041,19 +5936,19 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">744
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
@@ -6065,30 +5960,31 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">105
+</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -6099,31 +5995,31 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -6141,7 +6037,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">1897
 </t>
         </is>
       </c>
@@ -6159,23 +6055,26 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t xml:space="preserve">1813
+</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6192,7 +6091,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">14488
 </t>
         </is>
       </c>
@@ -6204,60 +6103,61 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">130
+</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -6269,7 +6169,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6281,7 +6181,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -6293,8 +6193,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
-</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -6305,8 +6204,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -6317,19 +6215,20 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6346,90 +6245,89 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-2 6
-</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">328
+</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">19249
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0401</t>
+          <t>028</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">2890
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -6441,24 +6339,25 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">1300
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1222
+</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -6470,18 +6369,18 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">870
+</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
@@ -6499,141 +6398,146 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
+          <t xml:space="preserve">23413
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t xml:space="preserve">1320
+</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">1886
+</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1247
+</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1230
+</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27914
+</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">814
-</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="X43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">946
+</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6656,24 +6560,24 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t xml:space="preserve">1239
+</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -6685,104 +6589,94 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">2286
 </t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">1810
+</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">151
+</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t xml:space="preserve">223
+</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="X44" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="n"/>
+      <c r="Y44" s="2" t="n"/>
+      <c r="Z44" s="2" t="n"/>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6795,129 +6689,97 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168711
+</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
-</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="n"/>
+          <t xml:space="preserve">102342
+</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11674
+</t>
+        </is>
+      </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">16912
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">1297
+</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">40844
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7335
-</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="n"/>
+      <c r="W45" s="2" t="n"/>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1848324382
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="n"/>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -6935,12 +6797,13 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">3117
+</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -6952,7 +6815,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2480
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
@@ -6964,7 +6827,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
@@ -6976,16 +6839,11 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -6994,13 +6852,13 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18256
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 8
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -7018,20 +6876,25 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">2062
 </t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="n"/>
+          <t xml:space="preserve">2216
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
@@ -7043,30 +6906,29 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2424
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="n"/>
+          <t xml:space="preserve">2242
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 7
-57
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">815
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -7077,37 +6939,6 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>Tot.</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">

--- a/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,34 +626,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94375
+          <t xml:space="preserve">837
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1312
+          <t xml:space="preserve">3182
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1242
+</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t xml:space="preserve">140
+</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">9124 11
 </t>
         </is>
       </c>
@@ -665,11 +668,16 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n"/>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 8
+</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">176
@@ -678,25 +686,25 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
+          <t xml:space="preserve">11785
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -708,19 +716,20 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t xml:space="preserve">637
+</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -731,7 +740,8 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t xml:space="preserve">277
+</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -755,10 +765,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -770,7 +784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">2135
 </t>
         </is>
       </c>
@@ -782,20 +796,15 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1874
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -813,17 +822,22 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900
-</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n"/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">205
@@ -838,19 +852,19 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -860,16 +874,21 @@
 </t>
         </is>
       </c>
-      <c r="W5" s="2" t="n"/>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">2725
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
+          <t xml:space="preserve">7261
 </t>
         </is>
       </c>
@@ -893,12 +912,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t xml:space="preserve">8316
+</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -922,32 +942,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">026
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1203
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -959,54 +984,55 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12329
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t xml:space="preserve">259
+</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16089
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -1018,13 +1044,13 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -1042,54 +1068,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14373
+          <t xml:space="preserve">1437
 </t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2330
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t xml:space="preserve">250
+</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">1123
+</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1100,13 +1129,13 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1673
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
@@ -1118,7 +1147,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1130,13 +1159,13 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20221
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
@@ -1148,25 +1177,20 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
-</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1241
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1779
+          <t xml:space="preserve">17729
 </t>
         </is>
       </c>
@@ -1190,7 +1214,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12972
+          <t xml:space="preserve">989716
 </t>
         </is>
       </c>
@@ -1202,13 +1226,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -1226,7 +1250,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1238,13 +1262,13 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1256,43 +1280,44 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1877
+          <t xml:space="preserve">877
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1332
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25241</t>
+          <t xml:space="preserve">954
+</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1315,7 +1340,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -1325,12 +1350,7 @@
 </t>
         </is>
       </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+      <c r="Z8" s="2" t="n"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1345,21 +1365,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16665
+          <t xml:space="preserve">1666
 </t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8526
-</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
+          <t xml:space="preserve">11526
+</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1368,7 +1399,12 @@
 </t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2112
+</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">155
@@ -1377,61 +1413,61 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">443
+          <t xml:space="preserve">440
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1963
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14409
+          <t xml:space="preserve">18409
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1629
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11388
+          <t xml:space="preserve">1388
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16173
+          <t xml:space="preserve">12173
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">18319
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13609
+          <t xml:space="preserve">3609
 </t>
         </is>
       </c>
@@ -1443,16 +1479,26 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11261
-</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="n"/>
+          <t xml:space="preserve">1261
+</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="n"/>
-      <c r="Y9" s="2" t="n"/>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114184
+</t>
+        </is>
+      </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
@@ -1470,19 +1516,20 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3051
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1499,13 +1546,13 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -1515,10 +1562,15 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="2" t="n"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -1528,10 +1580,15 @@
 </t>
         </is>
       </c>
-      <c r="N10" s="2" t="n"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -1549,19 +1606,19 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2722
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
@@ -1573,7 +1630,8 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">252
+</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1584,13 +1642,13 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">8259
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805
+          <t xml:space="preserve">805
 </t>
         </is>
       </c>
@@ -1614,7 +1672,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14450
+          <t xml:space="preserve">14451
 </t>
         </is>
       </c>
@@ -1632,7 +1690,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -1650,23 +1708,28 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">187
@@ -1675,76 +1738,81 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">2467
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t xml:space="preserve">279
+</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">23 08
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19819
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1975
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="n"/>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1759,13 +1827,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3836
-</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">1981
 </t>
         </is>
       </c>
@@ -1777,25 +1844,25 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -1807,13 +1874,14 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1836,13 +1904,13 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -1860,7 +1928,8 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85441</t>
+          <t xml:space="preserve">854
+</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1871,19 +1940,19 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12844
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -1895,7 +1964,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -1913,13 +1982,13 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">393567
+          <t xml:space="preserve">0856
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -1943,7 +2012,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -1955,19 +2024,19 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">053
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1985,14 +2054,19 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
-</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="n"/>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2016,19 +2090,19 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2064,13 +2138,13 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139740
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1325
+          <t xml:space="preserve">2325
 </t>
         </is>
       </c>
@@ -2094,17 +2168,22 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">57
@@ -2113,13 +2192,13 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -2131,14 +2210,13 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2155,7 +2233,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -2215,7 +2293,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335
+          <t xml:space="preserve">16433
 </t>
         </is>
       </c>
@@ -2227,13 +2305,13 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">2028
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2245,24 +2323,25 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">34
+</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
@@ -2274,13 +2353,19 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2304,13 +2389,13 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1638
+          <t xml:space="preserve">638
 </t>
         </is>
       </c>
@@ -2322,13 +2407,13 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12411
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2340,7 +2425,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">17410
 </t>
         </is>
       </c>
@@ -2364,37 +2449,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119928
+          <t xml:space="preserve">1992
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
+          <t xml:space="preserve">11299
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">9918
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1508
+          <t xml:space="preserve">508
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2413,43 +2498,42 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11009
-</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">1946
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
+          <t xml:space="preserve">10559
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4441
+          <t xml:space="preserve">44641
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">11230
 </t>
         </is>
       </c>
@@ -2461,13 +2545,14 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13687
+          <t xml:space="preserve">3687
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5334415</t>
+          <t xml:space="preserve">531
+</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2476,11 +2561,21 @@
 </t>
         </is>
       </c>
-      <c r="W16" s="2" t="n"/>
-      <c r="X16" s="2" t="n"/>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1151
+</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1375
+</t>
+        </is>
+      </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14551
+          <t xml:space="preserve">4551
 </t>
         </is>
       </c>
@@ -2504,12 +2599,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
@@ -2521,15 +2616,11 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12249
-</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">181
@@ -2538,7 +2629,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2548,28 +2639,23 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1202
-</t>
-        </is>
-      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2581,13 +2667,14 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t xml:space="preserve">1820
+</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2598,7 +2685,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -2610,7 +2697,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">2482
 </t>
         </is>
       </c>
@@ -2652,44 +2739,43 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
-</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1871
-</t>
-        </is>
-      </c>
+          <t>8441</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1713
+</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1395
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -2701,37 +2787,36 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2743,13 +2828,13 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -2767,13 +2852,13 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">4113
 </t>
         </is>
       </c>
@@ -2803,13 +2888,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14239
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">9225
 </t>
         </is>
       </c>
@@ -2821,19 +2905,19 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11248
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -2845,13 +2929,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
@@ -2863,7 +2946,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -2875,36 +2958,38 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">875
+</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">2618
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">12953
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t xml:space="preserve">540
+</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2915,7 +3000,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">16558
 </t>
         </is>
       </c>
@@ -2927,22 +3012,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>12</t>
@@ -2957,13 +3037,13 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568
+          <t xml:space="preserve">8568
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
@@ -2975,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -2987,7 +3067,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2999,31 +3079,26 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124080
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3041,19 +3116,19 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3065,7 +3140,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">95 1
 </t>
         </is>
       </c>
@@ -3077,7 +3152,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -3089,7 +3164,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672
+          <t xml:space="preserve">672
 </t>
         </is>
       </c>
@@ -3113,13 +3188,13 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14335
+          <t xml:space="preserve">433
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -3143,13 +3218,13 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3159,7 +3234,12 @@
 </t>
         </is>
       </c>
-      <c r="K21" s="2" t="n"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">188
@@ -3168,7 +3248,8 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3179,14 +3260,19 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1867
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n"/>
+          <t xml:space="preserve">867
+</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
@@ -3204,7 +3290,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -3216,13 +3302,14 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
@@ -3257,8 +3344,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374 0
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3267,12 +3353,7 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">245
@@ -3281,25 +3362,25 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3329,73 +3410,73 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">302
+</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">564
+</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1935
+</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1216
 </t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302
-</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1242
-</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1564
-</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1216
-</t>
-        </is>
-      </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -3425,19 +3506,19 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
+          <t xml:space="preserve">160274
 </t>
         </is>
       </c>
@@ -3455,48 +3536,58 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1355
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1952
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18828
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14372
+          <t xml:space="preserve">11372
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="n"/>
-      <c r="R23" s="2" t="n"/>
+          <t xml:space="preserve">15357
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1462
+</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11451
+</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -3505,7 +3596,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12952
+          <t xml:space="preserve">2952
 </t>
         </is>
       </c>
@@ -3515,17 +3606,27 @@
 </t>
         </is>
       </c>
-      <c r="V23" s="2" t="n"/>
-      <c r="W23" s="2" t="n"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2107
+</t>
+        </is>
+      </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11267
+          <t xml:space="preserve">2267
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14110
+          <t xml:space="preserve">18110
 </t>
         </is>
       </c>
@@ -3549,13 +3650,13 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3851
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -3567,19 +3668,19 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2246
+          <t xml:space="preserve">846
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -3591,11 +3692,16 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n"/>
+          <t xml:space="preserve">51
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -3604,26 +3710,31 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
-</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="n"/>
+          <t xml:space="preserve">874
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -3641,19 +3752,19 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1590
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3665,19 +3776,15 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
-</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1822
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">54
+</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3694,36 +3801,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13740
+          <t xml:space="preserve">3740
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">421
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3735,11 +3843,16 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n"/>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81414 6
+</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">195
@@ -3754,7 +3867,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -3766,30 +3879,31 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1313
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t xml:space="preserve">1040
+</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9569
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
@@ -3801,13 +3915,13 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3819,13 +3933,13 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17476
+          <t xml:space="preserve">1748
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">756
 </t>
         </is>
       </c>
@@ -3843,7 +3957,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
+          <t xml:space="preserve">3292
 </t>
         </is>
       </c>
@@ -3855,8 +3969,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3873,13 +3986,13 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1720
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3891,7 +4004,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -3903,24 +4016,25 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19492
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3944,38 +4058,35 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">68
+</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1811
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">176
@@ -3996,7 +4107,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">9522
 </t>
         </is>
       </c>
@@ -4008,13 +4119,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1924
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4030,10 +4141,15 @@
 </t>
         </is>
       </c>
-      <c r="I27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4045,7 +4161,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -4057,31 +4173,31 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4093,31 +4209,30 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1006
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">2098
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -4129,7 +4244,8 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">54
+</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4146,7 +4262,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93893
+          <t xml:space="preserve">2889
 </t>
         </is>
       </c>
@@ -4158,8 +4274,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -4176,25 +4291,25 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -4212,19 +4327,19 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">82813
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -4236,7 +4351,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -4248,26 +4363,25 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649
+          <t xml:space="preserve">649
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>556</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
@@ -4278,7 +4392,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -4302,7 +4416,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4085
+          <t xml:space="preserve">1408
 </t>
         </is>
       </c>
@@ -4314,52 +4428,51 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8229
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">203
 </t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1249
-</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">192
@@ -4368,7 +4481,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -4380,13 +4493,13 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -4398,7 +4511,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12265
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -4416,7 +4529,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -4428,13 +4541,13 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">81828
 </t>
         </is>
       </c>
@@ -4458,37 +4571,37 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18564
+          <t xml:space="preserve">118364
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1503
+          <t xml:space="preserve">1505
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">12241
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1525
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4506,13 +4619,13 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4524,55 +4637,55 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11032
+          <t xml:space="preserve">91034
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14419
+          <t xml:space="preserve">142419
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11137
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13328
+          <t xml:space="preserve">3328
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18231
+          <t xml:space="preserve">11231
 </t>
         </is>
       </c>
@@ -4584,14 +4697,12 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11243
-</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13998
-</t>
+          <t>394</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4614,12 +4725,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -4631,18 +4742,20 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t xml:space="preserve">105
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t xml:space="preserve">11824
+</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4657,10 +4770,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="n"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -4672,13 +4790,13 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>064</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4689,7 +4807,7 @@
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4701,52 +4819,46 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
+          <t xml:space="preserve">666
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="n"/>
       <c r="AA31" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4761,49 +4873,55 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">9437
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n"/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4815,23 +4933,28 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">4215
 </t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="n"/>
+          <t xml:space="preserve">884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">310
@@ -4840,7 +4963,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -4852,24 +4975,25 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">5606
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">2682
+</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">11288
 </t>
         </is>
       </c>
@@ -4881,13 +5005,13 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">1691
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11188
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -4905,48 +5029,54 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13970
+          <t xml:space="preserve">3971
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">2657
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n"/>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1011
 </t>
         </is>
       </c>
@@ -4958,12 +5088,13 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -4981,42 +5112,43 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">239
 </t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19477
+          <t xml:space="preserve">477
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -5028,7 +5160,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -5052,13 +5184,13 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3624
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -5076,19 +5208,19 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -5100,7 +5232,8 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">1024
+</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -5123,11 +5256,16 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1873
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="n"/>
+          <t xml:space="preserve">873
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">261
@@ -5136,31 +5274,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">78868
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0554</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -5171,19 +5310,19 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">2272
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
+          <t xml:space="preserve">18328
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -5207,55 +5346,55 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -5267,24 +5406,25 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2093
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t xml:space="preserve">834
+</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -5296,7 +5436,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -5308,25 +5448,25 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -5338,7 +5478,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -5362,19 +5502,18 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">9243
 </t>
         </is>
       </c>
@@ -5398,13 +5537,13 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5422,13 +5561,13 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -5440,25 +5579,25 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25938
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
+          <t xml:space="preserve">8225
 </t>
         </is>
       </c>
@@ -5470,7 +5609,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050
+          <t xml:space="preserve">2958
 </t>
         </is>
       </c>
@@ -5482,22 +5621,17 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">8468
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1782
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">782
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="n"/>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -5516,9 +5650,24 @@
 </t>
         </is>
       </c>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14501
+</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1202
+</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1255
+</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">492
@@ -5527,7 +5676,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924
+          <t xml:space="preserve">92241
 </t>
         </is>
       </c>
@@ -5545,7 +5694,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1608
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5555,11 +5704,21 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13965
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14325
+          <t xml:space="preserve">4375
 </t>
         </is>
       </c>
@@ -5571,7 +5730,7 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1396
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -5583,18 +5742,19 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>34311</t>
+          <t xml:space="preserve">3437
+</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657
+          <t xml:space="preserve">657
 </t>
         </is>
       </c>
@@ -5604,8 +5764,18 @@
 </t>
         </is>
       </c>
-      <c r="W37" s="2" t="n"/>
-      <c r="X37" s="2" t="n"/>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1271
+</t>
+        </is>
+      </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3966
@@ -5614,7 +5784,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3424
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -5650,7 +5820,8 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5661,22 +5832,28 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12111
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n"/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -5685,25 +5862,25 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19 3
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -5721,19 +5898,19 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1687
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
@@ -5745,7 +5922,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">2 24 2
 </t>
         </is>
       </c>
@@ -5757,13 +5934,13 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
+          <t xml:space="preserve">1793
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5781,19 +5958,19 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
+          <t xml:space="preserve">140018
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">4118
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -5805,7 +5982,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -5815,27 +5992,22 @@
 </t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">525
-</t>
-        </is>
-      </c>
+      <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -5847,7 +6019,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5859,19 +6031,19 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -5883,7 +6055,8 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t xml:space="preserve">5345
+</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -5894,34 +6067,29 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">12172
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18556
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="n"/>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -5942,13 +6110,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>94446</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -5960,30 +6127,31 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">539
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -6001,7 +6169,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -6013,13 +6181,13 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -6037,7 +6205,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
@@ -6049,31 +6217,31 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1906
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1813
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -6091,14 +6259,13 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14488
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6121,31 +6288,31 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -6181,7 +6348,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -6193,7 +6360,8 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t xml:space="preserve">584
+</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -6204,7 +6372,8 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -6215,7 +6384,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">12721
 </t>
         </is>
       </c>
@@ -6245,12 +6414,13 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -6262,13 +6432,13 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -6280,30 +6450,31 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>028</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -6315,7 +6486,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -6339,19 +6510,19 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">2282
 </t>
         </is>
       </c>
@@ -6363,24 +6534,25 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1104
+</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">187080
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -6398,19 +6570,19 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23413
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -6428,19 +6600,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6476,19 +6648,19 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -6500,32 +6672,26 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
-</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="n"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27914
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -6536,7 +6702,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -6554,25 +6720,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -6589,7 +6756,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">0808
 </t>
         </is>
       </c>
@@ -6613,17 +6780,20 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">2008
+</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t xml:space="preserve">1890
+</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -6634,13 +6804,13 @@
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2286
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6652,28 +6822,23 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18223
+</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="n"/>
       <c r="X44" s="2" t="n"/>
       <c r="Y44" s="2" t="n"/>
       <c r="Z44" s="2" t="n"/>
@@ -6691,92 +6856,132 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168711
-</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
+          <t xml:space="preserve">188411
+</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8411
+</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1740
+</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1602
+</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1056
+</t>
+        </is>
+      </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">28161
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">121804
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="n"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101092106191
+</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102342
+          <t xml:space="preserve">02041
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11674
+          <t xml:space="preserve">168084
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16912
+          <t xml:space="preserve">12572
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">12917
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">183179
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40844
+          <t xml:space="preserve">448414
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="n"/>
-      <c r="W45" s="2" t="n"/>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11222
+</t>
+        </is>
+      </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848324382
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="2" t="n"/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">815
+</t>
+        </is>
+      </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -6797,13 +7002,13 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
+          <t xml:space="preserve">5117
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -6815,35 +7020,40 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11226
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -6858,8 +7068,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -6876,13 +7085,13 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2062
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -6894,7 +7103,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
@@ -6906,28 +7115,23 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">2188
 </t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9247
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3182
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -644,7 +644,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -656,7 +656,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9124 11
+          <t xml:space="preserve">91124 1
 </t>
         </is>
       </c>
@@ -674,13 +674,13 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 8
+          <t xml:space="preserve">8 8 8
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1756
 </t>
         </is>
       </c>
@@ -692,7 +692,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11785
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -740,7 +740,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -784,7 +784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -796,18 +796,13 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">191
@@ -822,7 +817,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -832,12 +827,7 @@
 </t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
+      <c r="P5" s="2" t="n"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">205
@@ -864,7 +854,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -876,19 +866,19 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2725
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7261
+          <t xml:space="preserve">741
 </t>
         </is>
       </c>
@@ -912,7 +902,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8316
+          <t xml:space="preserve">4326
 </t>
         </is>
       </c>
@@ -942,25 +932,25 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">026
+          <t xml:space="preserve">096
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -1014,13 +1004,13 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">619
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1068,19 +1058,19 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437
+          <t xml:space="preserve">437
 </t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1092,13 +1082,13 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">1848
 </t>
         </is>
       </c>
@@ -1117,25 +1107,25 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">2620
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">876
 </t>
         </is>
       </c>
@@ -1190,7 +1180,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17729
+          <t xml:space="preserve">7279
 </t>
         </is>
       </c>
@@ -1214,7 +1204,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989716
+          <t xml:space="preserve">297 6
 </t>
         </is>
       </c>
@@ -1226,28 +1216,28 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">172
 </t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -1274,7 +1264,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1371,13 +1361,13 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11526
+          <t xml:space="preserve">1526
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1401,7 +1391,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -1437,7 +1427,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18409
+          <t xml:space="preserve">4409
 </t>
         </is>
       </c>
@@ -1455,13 +1445,13 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12173
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18319
+          <t xml:space="preserve">12319
 </t>
         </is>
       </c>
@@ -1489,16 +1479,21 @@
 </t>
         </is>
       </c>
-      <c r="X9" s="2" t="n"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114184
+          <t xml:space="preserve">1141024
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">388
 </t>
         </is>
       </c>
@@ -1546,28 +1541,18 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -1582,13 +1567,13 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">2193
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
@@ -1642,7 +1627,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -1654,7 +1639,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -1672,7 +1657,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14451
+          <t xml:space="preserve">24451
 </t>
         </is>
       </c>
@@ -1702,7 +1687,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1852
 </t>
         </is>
       </c>
@@ -1714,13 +1699,13 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -1738,7 +1723,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2467
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -1750,7 +1735,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1762,7 +1747,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 08
+          <t xml:space="preserve">25 8
 </t>
         </is>
       </c>
@@ -1774,13 +1759,13 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">587
 </t>
         </is>
       </c>
@@ -1792,7 +1777,8 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">247 16
+</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -1809,7 +1795,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -1827,12 +1813,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -1856,7 +1842,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1874,7 +1860,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -1958,13 +1944,13 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">977
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -1982,7 +1968,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0856
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -2000,7 +1986,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">2355
 </t>
         </is>
       </c>
@@ -2024,13 +2010,13 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">053
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2108,13 +2094,13 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -2144,7 +2130,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2325
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -2168,7 +2154,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2178,12 +2164,7 @@
 </t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+      <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">57
@@ -2198,7 +2179,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -2216,7 +2197,8 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2233,7 +2215,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2263,13 +2245,13 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -2293,7 +2275,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16433
+          <t xml:space="preserve">433
 </t>
         </is>
       </c>
@@ -2305,7 +2287,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -2317,19 +2299,19 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2341,7 +2323,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 8
+          <t xml:space="preserve">16 8
 </t>
         </is>
       </c>
@@ -2401,7 +2383,7 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
@@ -2425,7 +2407,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17410
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -2455,19 +2437,19 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11299
+          <t xml:space="preserve">192499
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9918
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
@@ -2483,7 +2465,12 @@
 </t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -2498,30 +2485,30 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>112</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
+          <t xml:space="preserve">9246
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10559
+          <t xml:space="preserve">1058
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44641
+          <t xml:space="preserve">4448
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -2533,7 +2520,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2599,12 +2586,13 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">398
+</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2620,7 +2608,12 @@
 </t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">181
@@ -2629,18 +2622,21 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -2655,7 +2651,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2673,7 +2669,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">282240
 </t>
         </is>
       </c>
@@ -2685,25 +2681,25 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2482
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -2715,13 +2711,13 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -2739,7 +2735,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2751,43 +2747,47 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>149</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1713
-</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2804,13 +2804,13 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2846,19 +2846,19 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">2506
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4113
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9225
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -2929,7 +2929,8 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2970,19 +2971,19 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2618
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12953
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -3000,7 +3001,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16558
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -3018,7 +3019,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -3037,13 +3038,13 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8568
+          <t xml:space="preserve">9568
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -3055,7 +3056,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3067,7 +3068,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3077,13 +3078,12 @@
 </t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -3104,19 +3104,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">2890
 </t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3128,13 +3128,13 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
+          <t xml:space="preserve">7072
 </t>
         </is>
       </c>
@@ -3152,8 +3152,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -3236,7 +3235,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3296,7 +3295,7 @@
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2089
 </t>
         </is>
       </c>
@@ -3320,7 +3319,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">8508
 </t>
         </is>
       </c>
@@ -3344,7 +3343,8 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>344</t>
+          <t xml:space="preserve">3741
+</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3353,7 +3353,11 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">245
@@ -3362,7 +3366,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1846
 </t>
         </is>
       </c>
@@ -3374,7 +3378,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3452,19 +3456,19 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1935
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -3476,7 +3480,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -3500,13 +3504,13 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">1551
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -3518,7 +3522,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160274
+          <t xml:space="preserve">6059
 </t>
         </is>
       </c>
@@ -3542,7 +3546,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">4953
 </t>
         </is>
       </c>
@@ -3566,25 +3570,25 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11372
+          <t xml:space="preserve">4372
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15357
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11451
+          <t xml:space="preserve">11431
 </t>
         </is>
       </c>
@@ -3608,13 +3612,13 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2107
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -3626,7 +3630,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18110
+          <t xml:space="preserve">14110
 </t>
         </is>
       </c>
@@ -3650,25 +3654,25 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -3680,7 +3684,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -3692,7 +3696,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -3716,7 +3720,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -3728,13 +3732,13 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3746,7 +3750,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23 8
 </t>
         </is>
       </c>
@@ -3807,19 +3811,19 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -3831,40 +3835,40 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 6
+</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81414 6
-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">204
@@ -3873,25 +3877,25 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">31 5
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -3903,19 +3907,19 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3927,7 +3931,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -3939,7 +3943,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -3998,7 +4002,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
@@ -4022,7 +4026,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">89 2
 </t>
         </is>
       </c>
@@ -4052,7 +4056,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -4064,7 +4068,7 @@
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -4107,25 +4111,24 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9522
+          <t xml:space="preserve">3548
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4137,13 +4140,13 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -4179,7 +4182,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
@@ -4197,7 +4200,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -4215,18 +4218,18 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1006
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>634</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -4238,7 +4241,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -4262,7 +4265,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -4274,7 +4277,8 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -4285,19 +4289,19 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4327,7 +4331,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82813
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -4339,7 +4343,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4369,7 +4373,7 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -4381,18 +4385,18 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -4416,30 +4420,29 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8229
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4481,7 +4484,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4493,7 +4496,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4511,13 +4514,13 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">2245
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1626
+          <t xml:space="preserve">624
 </t>
         </is>
       </c>
@@ -4541,19 +4544,19 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81828
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
@@ -4571,7 +4574,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118364
+          <t xml:space="preserve">118564
 </t>
         </is>
       </c>
@@ -4583,13 +4586,13 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
@@ -4607,7 +4610,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4625,7 +4628,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">9296
 </t>
         </is>
       </c>
@@ -4637,25 +4640,25 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91034
+          <t xml:space="preserve">1034
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142419
+          <t xml:space="preserve">4419
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">2385
 </t>
         </is>
       </c>
@@ -4679,13 +4682,13 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
@@ -4697,12 +4700,12 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>613</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>439</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4725,19 +4728,18 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>334</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>096</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4754,7 +4756,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11824
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -4770,15 +4772,10 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -4796,12 +4793,13 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t xml:space="preserve">884
+</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4819,7 +4817,8 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4830,13 +4829,13 @@
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">28246
 </t>
         </is>
       </c>
@@ -4848,13 +4847,13 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
@@ -4873,13 +4872,13 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9437
+          <t xml:space="preserve">1437
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">4128
 </t>
         </is>
       </c>
@@ -4891,7 +4890,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -4909,7 +4908,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -4921,85 +4920,85 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1285
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">566
+</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">19
 </t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4215
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5606
-</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2682
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11288
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -5011,7 +5010,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -5029,13 +5028,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3971
-</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
@@ -5047,7 +5045,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -5059,14 +5057,13 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -5076,7 +5073,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1011
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5118,7 +5115,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">2389
 </t>
         </is>
       </c>
@@ -5160,13 +5157,13 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">17276
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -5190,7 +5187,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -5208,7 +5205,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5232,7 +5229,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5274,7 +5271,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5286,19 +5283,19 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78868
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
@@ -5310,13 +5307,13 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2272
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18328
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -5340,7 +5337,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
@@ -5406,13 +5403,13 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
@@ -5448,19 +5445,19 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -5472,13 +5469,13 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5508,24 +5505,24 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">19 0 1
 </t>
         </is>
       </c>
@@ -5543,7 +5540,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
@@ -5561,7 +5558,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -5597,7 +5594,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
@@ -5609,19 +5606,19 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2958
+          <t xml:space="preserve">2580
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8468
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -5652,19 +5649,19 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14501
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">002
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -5676,7 +5673,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92241
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -5706,13 +5703,13 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -5730,7 +5727,7 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">1396
 </t>
         </is>
       </c>
@@ -5742,7 +5739,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">12560
 </t>
         </is>
       </c>
@@ -5832,7 +5829,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5844,13 +5841,12 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -5898,7 +5894,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -5910,7 +5906,7 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -5922,7 +5918,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 24 2
+          <t xml:space="preserve">224 1
 </t>
         </is>
       </c>
@@ -5934,7 +5930,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1793
+          <t xml:space="preserve">793
 </t>
         </is>
       </c>
@@ -5958,13 +5954,13 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140018
+          <t xml:space="preserve">4008
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4118
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -5982,20 +5978,20 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">1585
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1821
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -6007,7 +6003,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6019,7 +6015,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">2884
 </t>
         </is>
       </c>
@@ -6031,31 +6027,31 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5345
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
@@ -6079,13 +6075,13 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12172
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18556
+          <t xml:space="preserve">1855
 </t>
         </is>
       </c>
@@ -6110,7 +6106,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>94446</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6127,109 +6123,109 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1890
+</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">897
+</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2083
+</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1906
-</t>
-        </is>
-      </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
@@ -6241,7 +6237,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -6259,13 +6255,13 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">648
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>943</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6276,7 +6272,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -6288,25 +6284,25 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6384,13 +6380,13 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12721
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -6414,13 +6410,13 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">14645
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -6456,7 +6452,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -6510,22 +6506,22 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2282
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500
+</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">222
 </t>
         </is>
       </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">500
-</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2282
-</t>
-        </is>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">275
@@ -6540,13 +6536,13 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187080
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -6570,7 +6566,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
+          <t xml:space="preserve">341
 </t>
         </is>
       </c>
@@ -6612,7 +6608,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -6648,7 +6644,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -6683,15 +6679,10 @@
 </t>
         </is>
       </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+      <c r="W43" s="2" t="inlineStr"/>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>531</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -6720,7 +6711,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
@@ -6756,13 +6747,13 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0808
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -6780,26 +6771,24 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1098
 </t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
-</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -6810,7 +6799,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6822,19 +6811,19 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -6856,43 +6845,42 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188411
+          <t xml:space="preserve">1682111
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8411
+          <t xml:space="preserve">8251
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1833
 </t>
         </is>
       </c>
@@ -6904,87 +6892,91 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28161
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121804
+          <t xml:space="preserve">19104
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="n"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101092106191
+          <t xml:space="preserve">100921059
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02041
+          <t xml:space="preserve">0342
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168084
+          <t xml:space="preserve">1404
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12572
+          <t xml:space="preserve">2575
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12917
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183179
+          <t xml:space="preserve">13820
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">448414
+          <t xml:space="preserve">4840
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1822
+</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">815
 </t>
         </is>
       </c>
-      <c r="V45" s="2" t="n"/>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11222
-</t>
-        </is>
-      </c>
-      <c r="X45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -7002,7 +6994,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5117
+          <t xml:space="preserve">3117
 </t>
         </is>
       </c>
@@ -7026,7 +7018,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -7038,7 +7030,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11226
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -7050,7 +7042,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -7068,7 +7060,8 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -7085,7 +7078,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -7121,13 +7114,13 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">837
+          <t xml:space="preserve">437
 </t>
         </is>
       </c>
@@ -644,7 +644,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">11242
 </t>
         </is>
       </c>
@@ -656,7 +656,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91124 1
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -674,19 +674,19 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 8 8
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1756
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
@@ -740,16 +740,11 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">277
+</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="n"/>
       <c r="X4" s="2" t="n"/>
       <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
@@ -767,7 +762,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>621</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -796,13 +791,23 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">191
@@ -827,7 +832,12 @@
 </t>
         </is>
       </c>
-      <c r="P5" s="2" t="n"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">205
@@ -842,7 +852,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
@@ -854,7 +864,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -866,25 +876,25 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1240
+</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">741
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">741
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -902,8 +912,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4326
-</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -920,7 +929,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
@@ -938,19 +947,19 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">096
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">1006
 </t>
         </is>
       </c>
@@ -1010,7 +1019,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -1022,7 +1031,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1068,12 +1077,7 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">250
@@ -1088,11 +1092,16 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848
-</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n"/>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">49
@@ -1101,31 +1110,31 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">8726
 </t>
         </is>
       </c>
@@ -1137,7 +1146,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1155,7 +1164,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">1521
 </t>
         </is>
       </c>
@@ -1171,22 +1180,27 @@
 </t>
         </is>
       </c>
-      <c r="W7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7279
+          <t xml:space="preserve">779
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -1204,20 +1218,19 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297 6
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">2326
 </t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1228,7 +1241,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
@@ -1264,7 +1277,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1312,7 +1325,7 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1330,17 +1343,22 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1752
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">270
 </t>
         </is>
       </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="n"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1361,25 +1379,25 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1526
+          <t xml:space="preserve">8526
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">8225
 </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1391,7 +1409,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -1403,7 +1421,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
@@ -1445,13 +1463,13 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
+          <t xml:space="preserve">16173
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12319
+          <t xml:space="preserve">1319
 </t>
         </is>
       </c>
@@ -1481,19 +1499,19 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1295
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141024
+          <t xml:space="preserve">4024
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1541,18 +1559,28 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n"/>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -1567,7 +1595,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2193
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -1591,7 +1619,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
@@ -1657,7 +1685,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24451
+          <t xml:space="preserve">445
 </t>
         </is>
       </c>
@@ -1675,19 +1703,19 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -1699,13 +1727,13 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1723,68 +1751,66 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
+</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>8501</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">879
-</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25 8
-</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
-</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">850
-</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">587
-</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247 16
-</t>
-        </is>
-      </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1813,12 +1839,13 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t xml:space="preserve">383
+</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
@@ -1842,7 +1869,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1860,7 +1887,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1890,7 +1917,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -1938,13 +1965,13 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">1304
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
+          <t xml:space="preserve">11977
 </t>
         </is>
       </c>
@@ -1968,7 +1995,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
@@ -1986,7 +2013,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2355
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -2124,7 +2151,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
@@ -2154,7 +2181,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2164,7 +2191,12 @@
 </t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">57
@@ -2179,7 +2211,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -2197,7 +2229,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2227,7 +2259,7 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -2245,14 +2277,13 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2275,7 +2306,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">433
+          <t xml:space="preserve">1433
 </t>
         </is>
       </c>
@@ -2287,7 +2318,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2028
 </t>
         </is>
       </c>
@@ -2305,7 +2336,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -2323,7 +2354,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 8
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2335,7 +2366,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
@@ -2383,13 +2414,13 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
@@ -2401,7 +2432,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -2413,7 +2444,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -2431,13 +2462,13 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1992
+          <t xml:space="preserve">19928
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192499
+          <t xml:space="preserve">1499
 </t>
         </is>
       </c>
@@ -2455,54 +2486,48 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9246
+          <t xml:space="preserve">1946
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1058
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4448
+          <t xml:space="preserve">4441
 </t>
         </is>
       </c>
@@ -2520,13 +2545,13 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425
+          <t xml:space="preserve">10425
 </t>
         </is>
       </c>
@@ -2556,8 +2581,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2586,7 +2610,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">3998
 </t>
         </is>
       </c>
@@ -2610,31 +2634,38 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1115515
+</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">1202
+</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2651,7 +2682,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2669,19 +2700,19 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282240
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">1737
 </t>
         </is>
       </c>
@@ -2699,7 +2730,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2735,13 +2766,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -2753,7 +2783,8 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2764,19 +2795,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2787,30 +2818,31 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -2834,7 +2866,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">631
 </t>
         </is>
       </c>
@@ -2852,13 +2884,13 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2506
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -2888,7 +2920,8 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t xml:space="preserve">22234
+</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2929,13 +2962,13 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -2947,7 +2980,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
@@ -2971,7 +3004,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -3023,7 +3056,11 @@
 </t>
         </is>
       </c>
-      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>12</t>
@@ -3038,8 +3075,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9568
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3062,7 +3098,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -3078,10 +3114,16 @@
 </t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">244
+</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -3104,7 +3146,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -3116,13 +3158,13 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">12415
 </t>
         </is>
       </c>
@@ -3134,13 +3176,13 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7072
+          <t xml:space="preserve">707
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95 1
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -3152,7 +3194,8 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t xml:space="preserve">205
+</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -3241,22 +3284,22 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">867
@@ -3265,7 +3308,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3289,13 +3332,13 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3319,7 +3362,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8508
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -3343,37 +3386,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3741
+          <t xml:space="preserve">23746
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">2318
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">12475
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -3402,7 +3445,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
@@ -3444,7 +3487,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
+          <t xml:space="preserve">2564
 </t>
         </is>
       </c>
@@ -3456,7 +3499,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
@@ -3498,13 +3541,13 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19255
+          <t xml:space="preserve">1925
 </t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
@@ -3522,7 +3565,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6059
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
@@ -3540,13 +3583,13 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4953
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
@@ -3582,61 +3625,60 @@
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1462
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11431
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2952
+          <t xml:space="preserve">28952
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2267
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14110
+          <t xml:space="preserve">4110
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -3654,7 +3696,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">13985
 </t>
         </is>
       </c>
@@ -3666,25 +3708,25 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
@@ -3720,7 +3762,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -3738,7 +3780,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -3750,7 +3792,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 8
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -3762,7 +3804,7 @@
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -3784,7 +3826,12 @@
 </t>
         </is>
       </c>
-      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">54
@@ -3805,25 +3852,25 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">23740
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
@@ -3841,8 +3888,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3853,7 +3899,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3877,31 +3923,31 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 5
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -3913,7 +3959,7 @@
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -3931,7 +3977,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -3943,7 +3989,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -3961,7 +4007,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3292
+          <t xml:space="preserve">3298
 </t>
         </is>
       </c>
@@ -3973,7 +4019,8 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3990,7 +4037,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -4002,7 +4049,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4026,7 +4073,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89 2
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -4056,28 +4103,28 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">242
 </t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">218
@@ -4086,11 +4133,16 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1246
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">176
@@ -4111,13 +4163,13 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3548
+          <t xml:space="preserve">13544
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -4140,13 +4192,13 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4182,7 +4234,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -4218,13 +4270,14 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t xml:space="preserve">232
+</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -4241,8 +4294,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -4265,7 +4317,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">3893
 </t>
         </is>
       </c>
@@ -4313,7 +4365,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -4373,19 +4425,20 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
@@ -4402,8 +4455,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4426,12 +4478,14 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -4442,7 +4496,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -4454,7 +4508,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4466,7 +4520,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4484,7 +4538,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -4496,7 +4550,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4514,13 +4568,13 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
@@ -4532,7 +4586,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
@@ -4574,20 +4628,19 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118564
+          <t xml:space="preserve">18564
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1505
+          <t xml:space="preserve">1503
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4598,13 +4651,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">1525
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">1917
 </t>
         </is>
       </c>
@@ -4628,7 +4681,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9296
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4640,7 +4693,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
+          <t xml:space="preserve">1032
 </t>
         </is>
       </c>
@@ -4658,7 +4711,7 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
@@ -4682,7 +4735,7 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4700,12 +4753,14 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">1243
+</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t xml:space="preserve">3998
+</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4728,23 +4783,25 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">371
+</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>096</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4762,17 +4819,22 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -4817,13 +4879,13 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
@@ -4835,7 +4897,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -4847,17 +4909,22 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="2" t="n"/>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4872,13 +4939,13 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437
+          <t xml:space="preserve">457
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4128
+          <t xml:space="preserve">13528
 </t>
         </is>
       </c>
@@ -4890,13 +4957,13 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1669
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1126
 </t>
         </is>
       </c>
@@ -4908,7 +4975,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -4920,7 +4987,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4938,7 +5005,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -4950,8 +5017,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4980,19 +5046,19 @@
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">1237
 </t>
         </is>
       </c>
@@ -5004,13 +5070,13 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5028,12 +5094,13 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t xml:space="preserve">3979
+</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">337
 </t>
         </is>
       </c>
@@ -5068,12 +5135,13 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5115,7 +5183,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2389
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5127,43 +5195,43 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">477
+          <t xml:space="preserve">1477
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">258
 </t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17276
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -5181,7 +5249,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
+          <t xml:space="preserve">13624
 </t>
         </is>
       </c>
@@ -5211,7 +5279,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5223,13 +5291,13 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5295,7 +5363,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -5313,7 +5381,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -5367,7 +5435,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -5391,7 +5459,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5403,7 +5471,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5445,13 +5513,13 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -5499,13 +5567,14 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -5522,7 +5591,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 0 1
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -5534,13 +5603,13 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 8
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5558,7 +5627,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -5606,7 +5675,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -5618,7 +5687,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5628,7 +5697,11 @@
 </t>
         </is>
       </c>
-      <c r="Z36" s="2" t="n"/>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -5643,7 +5716,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116835
+          <t xml:space="preserve">1683
 </t>
         </is>
       </c>
@@ -5655,19 +5728,19 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">002
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">1492
 </t>
         </is>
       </c>
@@ -5691,7 +5764,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1028
 </t>
         </is>
       </c>
@@ -5709,7 +5782,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
@@ -5739,7 +5812,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12560
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
@@ -5799,7 +5872,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3367
+          <t xml:space="preserve">23267
 </t>
         </is>
       </c>
@@ -5817,7 +5890,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">1251
 </t>
         </is>
       </c>
@@ -5841,7 +5914,8 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -5858,13 +5932,13 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 3
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -5894,7 +5968,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -5906,7 +5980,7 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -5918,7 +5992,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224 1
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -5936,7 +6010,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -5954,7 +6028,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008
+          <t xml:space="preserve">14008
 </t>
         </is>
       </c>
@@ -5978,17 +6052,22 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1585
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1821
-</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">139
@@ -6015,7 +6094,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2884
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -6027,13 +6106,13 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -6045,7 +6124,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -6069,23 +6148,28 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="2" t="n"/>
+          <t xml:space="preserve">784
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">855
+</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -6106,30 +6190,31 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">2841
+</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">11290
 </t>
         </is>
       </c>
@@ -6165,7 +6250,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -6213,31 +6298,31 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2083
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">813
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -6255,24 +6340,25 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
+          <t xml:space="preserve">2448
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
@@ -6290,7 +6376,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -6392,7 +6478,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -6410,7 +6496,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14645
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
@@ -6434,7 +6520,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -6464,7 +6550,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6488,7 +6574,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -6506,13 +6592,13 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">1500
 </t>
         </is>
       </c>
@@ -6530,25 +6616,25 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
@@ -6566,7 +6652,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">341
+          <t xml:space="preserve">23413
 </t>
         </is>
       </c>
@@ -6578,7 +6664,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
@@ -6590,7 +6676,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -6632,19 +6718,19 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">1881
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -6662,7 +6748,7 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
@@ -6672,28 +6758,38 @@
 </t>
         </is>
       </c>
-      <c r="U43" s="2" t="n"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="W43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -6729,7 +6825,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -6753,7 +6849,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -6765,30 +6861,31 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">2041
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -6811,19 +6908,19 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -6845,42 +6942,42 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1682111
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8251
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t xml:space="preserve">1056
+</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1833
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -6892,27 +6989,31 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19104
-</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n"/>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1092
+</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100921059
+          <t xml:space="preserve">12181
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0342
-</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6923,54 +7024,50 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575
+          <t xml:space="preserve">1575
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13820
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840
+          <t xml:space="preserve">4240
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">11215
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1455
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822
-</t>
-        </is>
-      </c>
-      <c r="X45" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2312
+</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">483904
 </t>
         </is>
       </c>
@@ -7006,7 +7103,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -7018,13 +7115,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1041
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">11676
 </t>
         </is>
       </c>
@@ -7040,12 +7137,7 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -7066,7 +7158,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -7078,7 +7170,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -7114,13 +7206,13 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,122 +626,102 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">637
-</t>
+          <t>637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W4" s="2" t="n"/>
@@ -767,135 +747,113 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
-</t>
+          <t>741</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -917,140 +875,117 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1006
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
-</t>
+          <t>886</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
-</t>
+          <t>619</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1067,141 +1002,118 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8726
-</t>
+          <t>876</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">779
-</t>
+          <t>779</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1218,14 +1130,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1235,128 +1145,107 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
-</t>
+          <t>877</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1752
-</t>
+          <t>752</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1373,146 +1262,122 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
-</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8526
-</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225
-</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
+          <t>963</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4409
-</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16173
-</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
-</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
-</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
-</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4024
-</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,146 +1394,122 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,104 +1526,87 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">445
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>879</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1792,20 +1616,17 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -1815,14 +1636,12 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,146 +1658,122 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">383
-</t>
+          <t>383</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11977
-</t>
+          <t>977</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1995,146 +1790,122 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2151,134 +1922,112 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">509
-</t>
+          <t>509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2288,8 +2037,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2306,146 +2054,122 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1433
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
-</t>
+          <t>638</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2462,26 +2186,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19928
-</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
-</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
-</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2491,20 +2211,17 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -2515,68 +2232,57 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4441
-</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10425
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3687
-</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>531</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2586,14 +2292,12 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551
-</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2610,146 +2314,122 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
-</t>
+          <t>398</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115515
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
-</t>
+          <t>737</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2771,38 +2451,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2812,98 +2486,82 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2920,140 +2578,117 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22234
-</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -3080,140 +2715,117 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12415
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3230,146 +2842,122 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">433
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
+          <t>867</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3386,32 +2974,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23746
-</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12475
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3421,110 +3004,92 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3541,110 +3106,92 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925
-</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4372
-</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28952
-</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3654,32 +3201,27 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3696,146 +3238,122 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13985
-</t>
+          <t>385</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3852,38 +3370,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23740
-</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3893,104 +3405,87 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1748
-</t>
+          <t>748</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4007,146 +3502,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
-</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4163,8 +3634,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13544
-</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -4174,122 +3644,102 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -4299,8 +3749,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4317,140 +3766,117 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3893
-</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
-</t>
+          <t>649</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -4472,146 +3898,122 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>626</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4628,14 +4030,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18564
-</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1503
-</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4645,128 +4045,107 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1525
-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
-</t>
+          <t>917</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
-</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419
-</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
-</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3328
-</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
-</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4783,146 +4162,122 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
-</t>
+          <t>371</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>666</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4939,80 +4294,67 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">457
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13528
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1669
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -5022,62 +4364,52 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
-</t>
+          <t>566</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5094,38 +4426,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3979
-</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
-</t>
+          <t>337</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -5135,104 +4461,87 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477
-</t>
+          <t>477</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>776</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5249,146 +4558,122 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13624
-</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
-</t>
+          <t>873</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
-</t>
+          <t>786</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5405,146 +4690,122 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>879</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5561,140 +4822,117 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3989
-</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>723</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">782
-</t>
+          <t>782</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -5716,146 +4954,122 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
-</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
-</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
-</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1035
-</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
-</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1396
-</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3437
-</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">657
-</t>
+          <t>657</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
-</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3966
-</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5872,146 +5086,122 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23267
-</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
-</t>
+          <t>687</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
-</t>
+          <t>793</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -6028,146 +5218,122 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
-</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>545</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
-</t>
+          <t>784</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6184,146 +5350,122 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
-</t>
+          <t>744</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2841
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11290
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
-</t>
+          <t>813</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6340,146 +5482,122 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448
-</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
-</t>
+          <t>584</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6496,146 +5614,122 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6652,128 +5746,107 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23413
-</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>814</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
@@ -6783,14 +5856,12 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6807,74 +5878,62 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
-</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2041
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -6884,44 +5943,37 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="W44" s="2" t="n"/>
@@ -6947,68 +5999,57 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
-</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
-</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1092
-</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12181
-</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -7018,63 +6059,53 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575
-</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
-</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
-</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4240
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11215
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455
-</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
-</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">483904
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -7091,129 +6122,112 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11676
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="Y46" s="2" t="n"/>

--- a/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>442</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>222</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>328</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>310</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3263,34 +3263,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>193</t>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>408</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>913</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>181</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -5482,17 +5482,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>574</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>282</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -6100,7 +6100,7 @@
       <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">

--- a/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/209/Midpoint_Excel_with_OCR_Results.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>919</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>649</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>691</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>398</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>222</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>584</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>464</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -6100,7 +6100,7 @@
       <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -6132,49 +6132,49 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>202</t>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
